--- a/outputs_xlsx_solution/simple-branch.4-wide-NB-1.xlsx
+++ b/outputs_xlsx_solution/simple-branch.4-wide-NB-1.xlsx
@@ -114,6 +114,12 @@
   </si>
   <si>
     <t>Common Data Bus Stall (stalled because the CDB bandwidth is saturated)</t>
+  </si>
+  <si>
+    <t>FU Stall</t>
+  </si>
+  <si>
+    <t>Functional Unit Stall (stalled because the functional unit is busy)</t>
   </si>
 </sst>
 </file>
@@ -669,10 +675,26 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
         <v>25</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B16" t="s">
         <v>26</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
